--- a/data/trans_camb/IP19C04-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C04-Edad-trans_camb.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,39</t>
+          <t>0,0; 52,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,1</t>
+          <t>0,0; 31,56</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 12,96</t>
+          <t>-0,39; 13,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 7,03</t>
+          <t>-3,03; 6,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 9,58</t>
+          <t>-1,91; 9,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 7,4</t>
+          <t>-3,94; 7,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 5,39</t>
+          <t>-5,89; 4,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 4,42</t>
+          <t>-5,65; 5,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 7,95</t>
+          <t>-0,29; 8,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 4,56</t>
+          <t>-3,09; 4,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 5,26</t>
+          <t>-2,75; 5,09</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-33,78; 1533,91</t>
+          <t>-43,59; 1638,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-63,36; —</t>
+          <t>-65,82; 931,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-66,76; 386,16</t>
+          <t>-63,88; 444,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-82,69; 467,29</t>
+          <t>-86,5; 330,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 334,64</t>
+          <t>-100,0; 336,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 471,74</t>
+          <t>-14,92; 468,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-61,19; 265,97</t>
+          <t>-67,32; 255,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-52,63; 287,55</t>
+          <t>-54,07; 289,9</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 5,39</t>
+          <t>-3,85; 5,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 9,94</t>
+          <t>-0,33; 9,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 7,76</t>
+          <t>-2,3; 8,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 1,42</t>
+          <t>-10,34; 1,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 1,12</t>
+          <t>-10,01; 1,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,6; -0,63</t>
+          <t>-12,39; -0,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 1,78</t>
+          <t>-5,6; 2,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 4,1</t>
+          <t>-3,79; 4,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 1,17</t>
+          <t>-5,49; 1,68</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-61,02; 247,67</t>
+          <t>-54,67; 308,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 442,46</t>
+          <t>-13,47; 451,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-46,88; 344,66</t>
+          <t>-40,64; 368,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-75,8; 26,22</t>
+          <t>-78,64; 26,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-75,22; 25,49</t>
+          <t>-76,11; 25,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-85,33; 3,57</t>
+          <t>-86,67; 0,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-58,69; 37,25</t>
+          <t>-58,96; 49,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-38,32; 87,61</t>
+          <t>-40,51; 79,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-62,03; 24,5</t>
+          <t>-59,76; 30,39</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 2,39</t>
+          <t>-7,07; 2,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,22; -3,08</t>
+          <t>-10,67; -3,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,69; -1,35</t>
+          <t>-9,97; -1,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 3,61</t>
+          <t>-5,52; 3,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,42; -0,95</t>
+          <t>-8,23; -1,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,89; -0,85</t>
+          <t>-8,32; -1,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 1,52</t>
+          <t>-4,79; 1,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,27; -2,93</t>
+          <t>-8,12; -2,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,93; -2,35</t>
+          <t>-7,91; -2,03</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-64,57; 42,26</t>
+          <t>-65,26; 41,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-94,87; -40,52</t>
+          <t>-95,16; -43,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-87,42; -6,24</t>
+          <t>-87,63; -7,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-59,1; 72,25</t>
+          <t>-61,06; 74,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-88,85; -9,82</t>
+          <t>-89,26; -17,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-84,68; -3,26</t>
+          <t>-86,56; -14,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-53,65; 27,17</t>
+          <t>-52,33; 20,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-88,05; -45,03</t>
+          <t>-87,52; -44,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-82,68; -32,29</t>
+          <t>-83,63; -34,02</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 3,54</t>
+          <t>-2,28; 3,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 2,24</t>
+          <t>-3,43; 2,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 2,02</t>
+          <t>-3,96; 1,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 1,71</t>
+          <t>-4,17; 1,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,93; -0,43</t>
+          <t>-5,9; -0,39</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,55; -1,31</t>
+          <t>-6,42; -1,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 1,96</t>
+          <t>-2,43; 1,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 0,04</t>
+          <t>-3,89; 0,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,33; -0,66</t>
+          <t>-4,42; -0,68</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-33,59; 76,42</t>
+          <t>-33,09; 83,34</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-44,75; 51,72</t>
+          <t>-45,9; 51,23</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-52,89; 48,5</t>
+          <t>-54,1; 41,55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-48,69; 29,63</t>
+          <t>-49,19; 37,15</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-69,79; -6,4</t>
+          <t>-67,6; -3,83</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-74,94; -23,52</t>
+          <t>-74,75; -25,44</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-32,88; 34,52</t>
+          <t>-33,09; 32,03</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-52,74; 1,12</t>
+          <t>-51,35; 0,23</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-58,68; -11,61</t>
+          <t>-57,92; -11,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C04-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C04-Edad-trans_camb.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,66</t>
+          <t>0,0; 59,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,56</t>
+          <t>0,0; 30,05</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 13,55</t>
+          <t>0,43; 12,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 6,33</t>
+          <t>-2,86; 7,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 9,05</t>
+          <t>-1,63; 9,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 7,18</t>
+          <t>-3,76; 7,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 4,86</t>
+          <t>-5,67; 4,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 5,18</t>
+          <t>-5,43; 5,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 8,11</t>
+          <t>-0,26; 8,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 4,32</t>
+          <t>-2,91; 3,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 5,09</t>
+          <t>-2,34; 5,14</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-43,59; 1638,15</t>
+          <t>-30,8; 1120,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-84,61; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-65,82; 931,59</t>
+          <t>-56,8; 1470,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-63,88; 444,43</t>
+          <t>-64,04; 460,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-86,5; 330,65</t>
+          <t>-87,63; 292,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 336,67</t>
+          <t>-100,0; 373,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,92; 468,17</t>
+          <t>-11,07; 507,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-67,32; 255,35</t>
+          <t>-60,76; 216,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-54,07; 289,9</t>
+          <t>-51,77; 296,67</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 5,5</t>
+          <t>-3,94; 5,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 9,96</t>
+          <t>0,14; 10,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 8,08</t>
+          <t>-2,57; 7,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 1,41</t>
+          <t>-9,95; 1,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 1,09</t>
+          <t>-10,33; 0,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,39; -0,78</t>
+          <t>-11,82; -1,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 2,03</t>
+          <t>-5,47; 1,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 4,0</t>
+          <t>-3,91; 3,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 1,68</t>
+          <t>-5,75; 1,55</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-54,67; 308,29</t>
+          <t>-58,86; 218,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 451,57</t>
+          <t>-12,85; 439,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-40,64; 368,93</t>
+          <t>-46,77; 300,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-78,64; 26,69</t>
+          <t>-76,15; 30,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-76,11; 25,32</t>
+          <t>-77,38; 20,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-86,67; 0,06</t>
+          <t>-87,09; -13,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-58,96; 49,49</t>
+          <t>-59,66; 42,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-40,51; 79,67</t>
+          <t>-41,32; 74,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-59,76; 30,39</t>
+          <t>-61,54; 36,16</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 2,22</t>
+          <t>-7,42; 2,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,67; -3,13</t>
+          <t>-11,07; -3,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,97; -1,22</t>
+          <t>-9,62; -1,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 3,82</t>
+          <t>-5,28; 3,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,23; -1,09</t>
+          <t>-8,3; -1,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,32; -1,16</t>
+          <t>-7,92; -0,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 1,24</t>
+          <t>-5,18; 1,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,12; -2,96</t>
+          <t>-8,62; -3,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,91; -2,03</t>
+          <t>-7,93; -2,32</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-65,26; 41,21</t>
+          <t>-67,97; 39,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-95,16; -43,34</t>
+          <t>-95,33; -40,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-87,63; -7,0</t>
+          <t>-89,16; -10,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-61,06; 74,7</t>
+          <t>-62,49; 66,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-89,26; -17,8</t>
+          <t>-87,0; -0,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-86,56; -14,3</t>
+          <t>-83,56; -5,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-52,33; 20,75</t>
+          <t>-54,31; 26,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-87,52; -44,8</t>
+          <t>-88,4; -43,59</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-83,63; -34,02</t>
+          <t>-82,16; -36,29</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 3,65</t>
+          <t>-2,38; 3,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 2,15</t>
+          <t>-3,13; 2,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 1,8</t>
+          <t>-3,75; 1,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 1,86</t>
+          <t>-4,42; 1,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,9; -0,39</t>
+          <t>-6,0; -0,5</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,42; -1,56</t>
+          <t>-6,63; -1,3</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,68</t>
+          <t>-2,59; 1,51</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 0,02</t>
+          <t>-3,76; 0,04</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,42; -0,68</t>
+          <t>-4,36; -0,63</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-33,09; 83,34</t>
+          <t>-33,03; 91,8</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-45,9; 51,23</t>
+          <t>-44,12; 57,82</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-54,1; 41,55</t>
+          <t>-50,56; 44,19</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-49,19; 37,15</t>
+          <t>-51,94; 30,27</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-67,6; -3,83</t>
+          <t>-69,38; -7,03</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-74,75; -25,44</t>
+          <t>-75,33; -20,99</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-33,09; 32,03</t>
+          <t>-35,27; 27,65</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-51,35; 0,23</t>
+          <t>-49,38; 2,17</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-57,92; -11,27</t>
+          <t>-58,21; -10,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C04-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C04-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -634,24 +634,24 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>12,08</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13,3</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6,36</t>
+          <t>5,26</t>
         </is>
       </c>
     </row>
@@ -687,24 +687,24 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 51,33</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 59,37</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,05</t>
+          <t>0,0; 27,36</t>
         </is>
       </c>
     </row>
@@ -740,22 +740,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,48</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,4</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-0,72</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>6,07</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1,44</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,38</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,48</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,4</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,73</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>1,32</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 12,28</t>
+          <t>-4,36; 7,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 7,04</t>
+          <t>-5,75; 5,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 9,34</t>
+          <t>-6,15; 4,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 7,32</t>
+          <t>0,72; 12,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 4,71</t>
+          <t>-3,48; 7,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 5,05</t>
+          <t>-1,29; 9,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 8,26</t>
+          <t>0,03; 7,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 3,97</t>
+          <t>-2,82; 4,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 5,14</t>
+          <t>-2,33; 5,44</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>34,55%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-9,38%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-16,69%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>225,11%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>53,45%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>125,46%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>34,55%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-9,38%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-16,95%</t>
+          <t>126,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>38,03%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-30,8; 1120,92</t>
+          <t>-66,76; 386,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-84,61; —</t>
+          <t>-82,69; 467,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-56,8; 1470,19</t>
+          <t>-100,0; 367,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-64,04; 460,68</t>
+          <t>-33,78; 1533,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-87,63; 292,75</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 373,05</t>
+          <t>-63,78; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 507,45</t>
+          <t>-14,86; 471,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-60,76; 216,16</t>
+          <t>-61,19; 265,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-51,77; 296,67</t>
+          <t>-53,22; 296,07</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-3,96</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-4,17</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-5,92</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,85</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>4,73</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,52</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-3,96</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-4,17</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,92</t>
+          <t>2,66</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,05</t>
+          <t>-1,93</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 5,08</t>
+          <t>-10,12; 1,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 10,08</t>
+          <t>-10,15; 1,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 7,46</t>
+          <t>-11,57; -0,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 1,22</t>
+          <t>-4,56; 5,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 0,95</t>
+          <t>-0,46; 9,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,82; -1,25</t>
+          <t>-2,74; 7,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 1,85</t>
+          <t>-5,5; 1,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 3,76</t>
+          <t>-3,42; 4,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 1,55</t>
+          <t>-5,97; 1,4</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-42,13%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-44,43%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-63,03%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>18,42%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>102,92%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>54,78%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-42,13%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-44,43%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-63,01%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-28,98%</t>
+          <t>-27,34%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-58,86; 218,05</t>
+          <t>-75,8; 26,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 439,04</t>
+          <t>-75,22; 25,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-46,77; 300,91</t>
+          <t>-85,77; 6,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-76,15; 30,49</t>
+          <t>-61,02; 247,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-77,38; 20,01</t>
+          <t>-13,3; 442,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-87,09; -13,44</t>
+          <t>-46,53; 348,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-59,66; 42,69</t>
+          <t>-58,69; 37,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-41,32; 74,95</t>
+          <t>-38,32; 87,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-61,54; 36,16</t>
+          <t>-61,71; 28,69</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,04</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-4,5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-4,45</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-2,55</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-6,68</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-5,5</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-4,5</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,33</t>
+          <t>-6,17</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-4,9</t>
+          <t>-5,28</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 2,26</t>
+          <t>-5,39; 3,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,07; -3,07</t>
+          <t>-8,42; -0,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,62; -1,57</t>
+          <t>-8,09; -0,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 3,32</t>
+          <t>-7,15; 2,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,3; -1,06</t>
+          <t>-11,22; -3,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,92; -0,74</t>
+          <t>-10,21; -2,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 1,62</t>
+          <t>-5,0; 1,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,62; -3,03</t>
+          <t>-8,27; -2,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,93; -2,32</t>
+          <t>-8,14; -2,76</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-14,74%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-63,92%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-63,17%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-30,51%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-79,8%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-65,65%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-14,74%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-63,92%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-61,55%</t>
+          <t>-73,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-63,78%</t>
+          <t>-68,65%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-67,97; 39,26</t>
+          <t>-59,1; 72,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-95,33; -40,43</t>
+          <t>-88,85; -9,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-89,16; -10,39</t>
+          <t>-85,16; -5,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-62,49; 66,29</t>
+          <t>-64,57; 42,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-87,0; -0,44</t>
+          <t>-94,87; -40,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-83,56; -5,96</t>
+          <t>-89,63; -38,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-54,31; 26,79</t>
+          <t>-53,65; 27,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-88,4; -43,59</t>
+          <t>-88,05; -45,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-82,16; -36,29</t>
+          <t>-84,15; -41,81</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,35</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-3,16</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-3,95</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,43</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-0,57</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,15</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,35</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-3,16</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,86</t>
+          <t>-1,5</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,59</t>
+          <t>-2,78</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 3,68</t>
+          <t>-4,2; 1,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 2,41</t>
+          <t>-5,93; -0,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 1,74</t>
+          <t>-6,65; -1,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 1,56</t>
+          <t>-2,42; 3,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,0; -0,5</t>
+          <t>-3,16; 2,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,63; -1,3</t>
+          <t>-4,16; 1,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,51</t>
+          <t>-2,47; 1,96</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 0,04</t>
+          <t>-4,08; 0,04</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,36; -0,63</t>
+          <t>-4,5; -0,83</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-19,07%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-44,67%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-55,8%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>7,35%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-9,68%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-19,74%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-19,07%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-44,67%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-54,51%</t>
+          <t>-25,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-40,08%</t>
+          <t>-42,97%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-33,03; 91,8</t>
+          <t>-48,69; 29,63</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-44,12; 57,82</t>
+          <t>-69,79; -6,4</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-50,56; 44,19</t>
+          <t>-75,65; -24,78</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-51,94; 30,27</t>
+          <t>-33,59; 76,42</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-69,38; -7,03</t>
+          <t>-44,75; 51,72</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-75,33; -20,99</t>
+          <t>-56,75; 33,74</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-35,27; 27,65</t>
+          <t>-32,88; 34,52</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-49,38; 2,17</t>
+          <t>-52,74; 1,12</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-58,21; -10,17</t>
+          <t>-60,42; -14,97</t>
         </is>
       </c>
     </row>
